--- a/ops/label-generator/templates/007-PI-sea-canonical-v1.xlsx
+++ b/ops/label-generator/templates/007-PI-sea-canonical-v1.xlsx
@@ -44,7 +44,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Administrator</author>
+    <author>BYL Synthetic Fixture</author>
   </authors>
   <commentList>
     <comment ref="H4" authorId="0">
@@ -100,7 +100,7 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Administrator</author>
+    <author>BYL Synthetic Fixture</author>
   </authors>
   <commentList>
     <comment ref="F4" authorId="0">
@@ -156,7 +156,7 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Administrator</author>
+    <author>BYL Synthetic Fixture</author>
   </authors>
   <commentList>
     <comment ref="G4" authorId="0">
@@ -212,7 +212,7 @@
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Administrator</author>
+    <author>BYL Synthetic Fixture</author>
   </authors>
   <commentList>
     <comment ref="G4" authorId="0">
